--- a/main/StructureDefinition-bc-organization-clinic-legal-name-extension.xlsx
+++ b/main/StructureDefinition-bc-organization-clinic-legal-name-extension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-30T21:39:06+00:00</t>
+    <t>2026-04-01T23:28:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1239,7 +1239,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>97</v>
       </c>
@@ -1655,7 +1655,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>112</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>118</v>
       </c>
@@ -2174,7 +2174,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>123</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>125</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>130</v>
       </c>
@@ -2487,7 +2487,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>135</v>
       </c>
@@ -2802,12 +2802,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AK19">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
